--- a/docs/insumos/banco-v3-ejecutivo-y-operativo.xlsx
+++ b/docs/insumos/banco-v3-ejecutivo-y-operativo.xlsx
@@ -3119,7 +3119,7 @@
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>Me quedo si me avisan con tiempo Opción Clave</t>
+          <t>Me quedo si me avisan con tiempo</t>
         </is>
       </c>
       <c r="C53" s="7" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="B146" s="7" t="inlineStr">
         <is>
-          <t>No digo nada, no es mi área Opción Clave</t>
+          <t>No digo nada, no es mi área</t>
         </is>
       </c>
       <c r="C146" s="7" t="n">

--- a/docs/insumos/banco-v3-ejecutivo-y-operativo.xlsx
+++ b/docs/insumos/banco-v3-ejecutivo-y-operativo.xlsx
@@ -548,7 +548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:K54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -560,6 +560,8 @@
     <col width="26" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -569,6 +571,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -615,6 +618,16 @@
           <t>Nota interna (opcional)</t>
         </is>
       </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Fórmula de puntaje (solo V)</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Usa los rangos de (solo V)</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
@@ -660,6 +673,16 @@
       <c r="I4" s="6" t="inlineStr">
         <is>
           <t>Guía para el evaluador. El candidato nunca la ve.</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>Si el ítem V no se puntúa por tramos: la fórmula, en palabras.</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>Si el ítem V usa la tabla de otra pregunta: su código.</t>
         </is>
       </c>
     </row>
@@ -720,6 +743,11 @@
       <c r="G6" s="7" t="n"/>
       <c r="H6" s="7" t="n"/>
       <c r="I6" s="7" t="n"/>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>(campos llenos ÷ 5) × 3</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -869,6 +897,11 @@
       <c r="G11" s="7" t="n"/>
       <c r="H11" s="7" t="n"/>
       <c r="I11" s="7" t="n"/>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>(campos completos ÷ 9) × 3</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -1602,6 +1635,11 @@
       <c r="G36" s="7" t="n"/>
       <c r="H36" s="7" t="n"/>
       <c r="I36" s="7" t="n"/>
+      <c r="K36" s="7" t="inlineStr">
+        <is>
+          <t>D57</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
@@ -2072,6 +2110,11 @@
       <c r="G52" s="7" t="n"/>
       <c r="H52" s="7" t="n"/>
       <c r="I52" s="7" t="n"/>
+      <c r="K52" s="7" t="inlineStr">
+        <is>
+          <t>D84</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
